--- a/Promedios_mensuales/machala_promediostotal.xlsx
+++ b/Promedios_mensuales/machala_promediostotal.xlsx
@@ -659,14 +659,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>PERIODO: JULIO DE 2025</t>
+          <t>PERIODO:JULIO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 06/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 26/08/2025</t>
         </is>
       </c>
     </row>

--- a/Promedios_mensuales/machala_promediostotal.xlsx
+++ b/Promedios_mensuales/machala_promediostotal.xlsx
@@ -652,7 +652,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>CIUDAD:TAMBO</t>
+          <t>CIUDAD:MACHALA</t>
         </is>
       </c>
     </row>
